--- a/data/produtoshospitais.xlsx
+++ b/data/produtoshospitais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lfsoa\Desktop\Nutri_Hospital\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512EEA2C-4562-4230-8250-4930B125B555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28031F04-E28C-47C2-BD40-CD745D390D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="79530" yWindow="285" windowWidth="18570" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="76680" yWindow="165" windowWidth="38640" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="produtos_hospital" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
-  <si>
-    <t>hospital_nome</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="40">
   <si>
     <t>produto</t>
   </si>
@@ -31,7 +28,118 @@
     <t>quantidade</t>
   </si>
   <si>
-    <t>id_hospital</t>
+    <t>id</t>
+  </si>
+  <si>
+    <t>hospital_id</t>
+  </si>
+  <si>
+    <t>nome_hospital</t>
+  </si>
+  <si>
+    <t>marca_planilha</t>
+  </si>
+  <si>
+    <t>CASA DE SAÚDE SÃO FRANCISCO DE ASSIS</t>
+  </si>
+  <si>
+    <t>PRODIET</t>
+  </si>
+  <si>
+    <t>ENTERFIBER PREBIOTIC (FIBRAS SOLUVEIS)</t>
+  </si>
+  <si>
+    <t>TROPHIC PROTEIN (SF)</t>
+  </si>
+  <si>
+    <t>COMPLEXO DE SAÚDE SÃO JOÃO DE DEUS</t>
+  </si>
+  <si>
+    <t>DANONE</t>
+  </si>
+  <si>
+    <t>fresubim</t>
+  </si>
+  <si>
+    <t>SANTA CASA DE ARCOS</t>
+  </si>
+  <si>
+    <t>FRESENIUS</t>
+  </si>
+  <si>
+    <t>FRESUBIN HP ENERGY FIBRE</t>
+  </si>
+  <si>
+    <t>DIBEN 1.5</t>
+  </si>
+  <si>
+    <t>FRESUBIN ENERGY</t>
+  </si>
+  <si>
+    <t>FRESUBIN ENERGY HP</t>
+  </si>
+  <si>
+    <t>SANTA CASA DE BOM DESPACHO</t>
+  </si>
+  <si>
+    <t>FRESUBIN HP 2.0</t>
+  </si>
+  <si>
+    <t>COMPLEXO HOSPITALAR DE BRUMADINHO (VALDEMAR DE ASSIS BARCELOS</t>
+  </si>
+  <si>
+    <t>DIBEN</t>
+  </si>
+  <si>
+    <t>FRESUBIN HP</t>
+  </si>
+  <si>
+    <t>FRESUBIN</t>
+  </si>
+  <si>
+    <t>SANTA CASA DE CAMPO BELO</t>
+  </si>
+  <si>
+    <t>INSTANTH CLEAR (TEXTURA NECTAR)</t>
+  </si>
+  <si>
+    <t>HOSPITAL CARLOS CHAGAS</t>
+  </si>
+  <si>
+    <t>TROPHIC SOYA</t>
+  </si>
+  <si>
+    <t>SANTA CASA DE CARIDADE DE CAPITÓLIO</t>
+  </si>
+  <si>
+    <t>TROPHIC 1.5 (RTH/SA)</t>
+  </si>
+  <si>
+    <t>TROPHIC BASIC (RTH E SA)</t>
+  </si>
+  <si>
+    <t>SANTA CASA DE CARMO DA MATA</t>
+  </si>
+  <si>
+    <t>FRESUBIN ORIGINAL</t>
+  </si>
+  <si>
+    <t>SANTA CASA DE CLAUDIO</t>
+  </si>
+  <si>
+    <t>NUTRI ENTERAL 1.5</t>
+  </si>
+  <si>
+    <t>NUTRISON PROTEIN PLUS</t>
+  </si>
+  <si>
+    <t>NUTRISON ADVANCE DIASON</t>
+  </si>
+  <si>
+    <t>HOSPITAL SANTO ANTÔNIO</t>
+  </si>
+  <si>
+    <t>SURVIMED OPD HN</t>
   </si>
 </sst>
 </file>
@@ -67,7 +175,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -371,21 +480,587 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
         <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>14</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>7</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>7</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <v>35</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <v>35</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <v>35</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
+        <v>35</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <v>11</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1">
+        <v>8</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
+        <v>8</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <v>9</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
+        <v>10</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1">
+        <v>10</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1">
+        <v>10</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1">
+        <v>42</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1">
+        <v>42</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
+        <v>42</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1">
+        <v>42</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
